--- a/event_booking_forms/037_free_movie_ticket--event_booking_forms.xlsx
+++ b/event_booking_forms/037_free_movie_ticket--event_booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ticket_type</t>
+          <t>ticket_type_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ticket Type</t>
+          <t>Ticket Type 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ticket_price</t>
+          <t>ticket_price_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ticket Price</t>
+          <t>Ticket Price 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>event_end_time</t>
+          <t>event_end_time_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Event End Time</t>
+          <t>Event End Time 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>event_organizer</t>
+          <t>event_organizer_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Event Organiser</t>
+          <t>Event Organizer 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ticket_count</t>
+          <t>ticket_count_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ticket Count</t>
+          <t>Ticket Count 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1113,7 +1113,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ticket_type_choices</t>
+          <t>ticket_type_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1130,7 +1130,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ticket_type_choices</t>
+          <t>ticket_type_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>event_organizer_choices</t>
+          <t>event_organizer_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>event_organizer_choices</t>
+          <t>event_organizer_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
